--- a/src/app/modules/dashboard/excel_files/whole-food-plant-based-pasta-recipes.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-food-plant-based-pasta-recipes.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'pasta', 'bowls', 'salads']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
